--- a/sampleprojects/TestProject/excel/Test_map.xlsx
+++ b/sampleprojects/TestProject/excel/Test_map.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8" uniqueCount="8">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="17" uniqueCount="17">
   <si>
     <t>MAP: Test</t>
   </si>
@@ -38,6 +38,33 @@
   </si>
   <si>
     <t>integer</t>
+  </si>
+  <si>
+    <t>## CREATE ENTITIES (entity | tag | id | list)</t>
+  </si>
+  <si>
+    <t>job</t>
+  </si>
+  <si>
+    <t>id</t>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t>## ENTITIES (name | number: 1 or *)</t>
+  </si>
+  <si>
+    <t>1</t>
+  </si>
+  <si>
+    <t>*</t>
+  </si>
+  <si>
+    <t>## INITIALIZATION (entity | push)</t>
+  </si>
+  <si>
+    <t>true</t>
   </si>
 </sst>
 </file>
@@ -458,6 +485,88 @@
         <v>7</v>
       </c>
     </row>
+    <row r="4">
+      <c r="A4" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="B4" s="6"/>
+      <c r="C4" s="6"/>
+      <c r="D4" s="6"/>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="D5" s="2" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="D6" s="2" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="B7" s="6"/>
+      <c r="C7" s="6"/>
+      <c r="D7" s="6"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="C8" s="2"/>
+      <c r="D8" s="2"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="B9" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="C9" s="2"/>
+      <c r="D9" s="2"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="B10" s="6"/>
+      <c r="C10" s="6"/>
+      <c r="D10" s="6"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="B11" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="C11" s="2"/>
+      <c r="D11" s="2"/>
+    </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A1:D1"/>
